--- a/BSE/bse_daily.xlsx
+++ b/BSE/bse_daily.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1460"/>
+  <dimension ref="A1:E1461"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39836,6 +39836,33 @@
         </is>
       </c>
     </row>
+    <row r="1461">
+      <c r="A1461" t="inlineStr">
+        <is>
+          <t>16 Feb 2026</t>
+        </is>
+      </c>
+      <c r="B1461" t="inlineStr">
+        <is>
+          <t>4919</t>
+        </is>
+      </c>
+      <c r="C1461" t="inlineStr">
+        <is>
+          <t>29,40,812</t>
+        </is>
+      </c>
+      <c r="D1461" t="inlineStr">
+        <is>
+          <t>82,17,71,765</t>
+        </is>
+      </c>
+      <c r="E1461" t="inlineStr">
+        <is>
+          <t>7,505.87</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BSE/bse_daily.xlsx
+++ b/BSE/bse_daily.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1461"/>
+  <dimension ref="A1:E1462"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39863,6 +39863,33 @@
         </is>
       </c>
     </row>
+    <row r="1462">
+      <c r="A1462" t="inlineStr">
+        <is>
+          <t>17 Feb 2026</t>
+        </is>
+      </c>
+      <c r="B1462" t="inlineStr">
+        <is>
+          <t>4756</t>
+        </is>
+      </c>
+      <c r="C1462" t="inlineStr">
+        <is>
+          <t>26,46,213</t>
+        </is>
+      </c>
+      <c r="D1462" t="inlineStr">
+        <is>
+          <t>84,76,28,545</t>
+        </is>
+      </c>
+      <c r="E1462" t="inlineStr">
+        <is>
+          <t>6,866.89</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BSE/bse_daily.xlsx
+++ b/BSE/bse_daily.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1462"/>
+  <dimension ref="A1:E1464"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39890,6 +39890,60 @@
         </is>
       </c>
     </row>
+    <row r="1463">
+      <c r="A1463" t="inlineStr">
+        <is>
+          <t>18 Feb 2026</t>
+        </is>
+      </c>
+      <c r="B1463" t="inlineStr">
+        <is>
+          <t>4787</t>
+        </is>
+      </c>
+      <c r="C1463" t="inlineStr">
+        <is>
+          <t>2,796,101</t>
+        </is>
+      </c>
+      <c r="D1463" t="inlineStr">
+        <is>
+          <t>787,176,221</t>
+        </is>
+      </c>
+      <c r="E1463" t="inlineStr">
+        <is>
+          <t>7,022.73</t>
+        </is>
+      </c>
+    </row>
+    <row r="1464">
+      <c r="A1464" t="inlineStr">
+        <is>
+          <t>19 Feb 2026</t>
+        </is>
+      </c>
+      <c r="B1464" t="inlineStr">
+        <is>
+          <t>4726</t>
+        </is>
+      </c>
+      <c r="C1464" t="inlineStr">
+        <is>
+          <t>2,910,064</t>
+        </is>
+      </c>
+      <c r="D1464" t="inlineStr">
+        <is>
+          <t>672,893,186</t>
+        </is>
+      </c>
+      <c r="E1464" t="inlineStr">
+        <is>
+          <t>7,645.26</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BSE/bse_daily.xlsx
+++ b/BSE/bse_daily.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1464"/>
+  <dimension ref="A1:E1465"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39944,6 +39944,33 @@
         </is>
       </c>
     </row>
+    <row r="1465">
+      <c r="A1465" t="inlineStr">
+        <is>
+          <t>20 Feb 2026</t>
+        </is>
+      </c>
+      <c r="B1465" t="inlineStr">
+        <is>
+          <t>4715</t>
+        </is>
+      </c>
+      <c r="C1465" t="inlineStr">
+        <is>
+          <t>26,29,286</t>
+        </is>
+      </c>
+      <c r="D1465" t="inlineStr">
+        <is>
+          <t>71,91,05,378</t>
+        </is>
+      </c>
+      <c r="E1465" t="inlineStr">
+        <is>
+          <t>7,562.21</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BSE/bse_daily.xlsx
+++ b/BSE/bse_daily.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1465"/>
+  <dimension ref="A1:E1475"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39971,6 +39971,276 @@
         </is>
       </c>
     </row>
+    <row r="1466">
+      <c r="A1466" t="inlineStr">
+        <is>
+          <t>23 Feb 2026</t>
+        </is>
+      </c>
+      <c r="B1466" t="inlineStr">
+        <is>
+          <t>4917</t>
+        </is>
+      </c>
+      <c r="C1466" t="inlineStr">
+        <is>
+          <t>3,070,727</t>
+        </is>
+      </c>
+      <c r="D1466" t="inlineStr">
+        <is>
+          <t>815,371,136</t>
+        </is>
+      </c>
+      <c r="E1466" t="inlineStr">
+        <is>
+          <t>7,379.46</t>
+        </is>
+      </c>
+    </row>
+    <row r="1467">
+      <c r="A1467" t="inlineStr">
+        <is>
+          <t>24 Feb 2026</t>
+        </is>
+      </c>
+      <c r="B1467" t="inlineStr">
+        <is>
+          <t>4766</t>
+        </is>
+      </c>
+      <c r="C1467" t="inlineStr">
+        <is>
+          <t>3,008,138</t>
+        </is>
+      </c>
+      <c r="D1467" t="inlineStr">
+        <is>
+          <t>761,471,467</t>
+        </is>
+      </c>
+      <c r="E1467" t="inlineStr">
+        <is>
+          <t>7,307.02</t>
+        </is>
+      </c>
+    </row>
+    <row r="1468">
+      <c r="A1468" t="inlineStr">
+        <is>
+          <t>25 Feb 2026</t>
+        </is>
+      </c>
+      <c r="B1468" t="inlineStr">
+        <is>
+          <t>4789</t>
+        </is>
+      </c>
+      <c r="C1468" t="inlineStr">
+        <is>
+          <t>3,130,311</t>
+        </is>
+      </c>
+      <c r="D1468" t="inlineStr">
+        <is>
+          <t>1,093,096,198</t>
+        </is>
+      </c>
+      <c r="E1468" t="inlineStr">
+        <is>
+          <t>10,464.47</t>
+        </is>
+      </c>
+    </row>
+    <row r="1469">
+      <c r="A1469" t="inlineStr">
+        <is>
+          <t>26 Feb 2026</t>
+        </is>
+      </c>
+      <c r="B1469" t="inlineStr">
+        <is>
+          <t>4744</t>
+        </is>
+      </c>
+      <c r="C1469" t="inlineStr">
+        <is>
+          <t>2,987,857</t>
+        </is>
+      </c>
+      <c r="D1469" t="inlineStr">
+        <is>
+          <t>935,149,897</t>
+        </is>
+      </c>
+      <c r="E1469" t="inlineStr">
+        <is>
+          <t>10,029.74</t>
+        </is>
+      </c>
+    </row>
+    <row r="1470">
+      <c r="A1470" t="inlineStr">
+        <is>
+          <t>27 Feb 2026</t>
+        </is>
+      </c>
+      <c r="B1470" t="inlineStr">
+        <is>
+          <t>4770</t>
+        </is>
+      </c>
+      <c r="C1470" t="inlineStr">
+        <is>
+          <t>3,339,572</t>
+        </is>
+      </c>
+      <c r="D1470" t="inlineStr">
+        <is>
+          <t>826,414,135</t>
+        </is>
+      </c>
+      <c r="E1470" t="inlineStr">
+        <is>
+          <t>8,002.44</t>
+        </is>
+      </c>
+    </row>
+    <row r="1471">
+      <c r="A1471" t="inlineStr">
+        <is>
+          <t>02 Mar 2026</t>
+        </is>
+      </c>
+      <c r="B1471" t="inlineStr">
+        <is>
+          <t>4987</t>
+        </is>
+      </c>
+      <c r="C1471" t="inlineStr">
+        <is>
+          <t>5,030,301</t>
+        </is>
+      </c>
+      <c r="D1471" t="inlineStr">
+        <is>
+          <t>1,087,837,017</t>
+        </is>
+      </c>
+      <c r="E1471" t="inlineStr">
+        <is>
+          <t>11,505.69</t>
+        </is>
+      </c>
+    </row>
+    <row r="1472">
+      <c r="A1472" t="inlineStr">
+        <is>
+          <t>04 Mar 2026</t>
+        </is>
+      </c>
+      <c r="B1472" t="inlineStr">
+        <is>
+          <t>4927</t>
+        </is>
+      </c>
+      <c r="C1472" t="inlineStr">
+        <is>
+          <t>4,662,231</t>
+        </is>
+      </c>
+      <c r="D1472" t="inlineStr">
+        <is>
+          <t>989,292,516</t>
+        </is>
+      </c>
+      <c r="E1472" t="inlineStr">
+        <is>
+          <t>10,418.94</t>
+        </is>
+      </c>
+    </row>
+    <row r="1473">
+      <c r="A1473" t="inlineStr">
+        <is>
+          <t>05 Mar 2026</t>
+        </is>
+      </c>
+      <c r="B1473" t="inlineStr">
+        <is>
+          <t>4852</t>
+        </is>
+      </c>
+      <c r="C1473" t="inlineStr">
+        <is>
+          <t>3,746,610</t>
+        </is>
+      </c>
+      <c r="D1473" t="inlineStr">
+        <is>
+          <t>801,361,298</t>
+        </is>
+      </c>
+      <c r="E1473" t="inlineStr">
+        <is>
+          <t>9,258.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1474">
+      <c r="A1474" t="inlineStr">
+        <is>
+          <t>06 Mar 2026</t>
+        </is>
+      </c>
+      <c r="B1474" t="inlineStr">
+        <is>
+          <t>4797</t>
+        </is>
+      </c>
+      <c r="C1474" t="inlineStr">
+        <is>
+          <t>3,118,392</t>
+        </is>
+      </c>
+      <c r="D1474" t="inlineStr">
+        <is>
+          <t>724,053,822</t>
+        </is>
+      </c>
+      <c r="E1474" t="inlineStr">
+        <is>
+          <t>8,028.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="1475">
+      <c r="A1475" t="inlineStr">
+        <is>
+          <t>09 Mar 2026</t>
+        </is>
+      </c>
+      <c r="B1475" t="inlineStr">
+        <is>
+          <t>5050</t>
+        </is>
+      </c>
+      <c r="C1475" t="inlineStr">
+        <is>
+          <t>4,135,156</t>
+        </is>
+      </c>
+      <c r="D1475" t="inlineStr">
+        <is>
+          <t>760,334,542</t>
+        </is>
+      </c>
+      <c r="E1475" t="inlineStr">
+        <is>
+          <t>9,658.54</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BSE/bse_daily.xlsx
+++ b/BSE/bse_daily.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1475"/>
+  <dimension ref="A1:E1477"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40241,6 +40241,60 @@
         </is>
       </c>
     </row>
+    <row r="1476">
+      <c r="A1476" t="inlineStr">
+        <is>
+          <t>10 Mar 2026</t>
+        </is>
+      </c>
+      <c r="B1476" t="inlineStr">
+        <is>
+          <t>4901</t>
+        </is>
+      </c>
+      <c r="C1476" t="inlineStr">
+        <is>
+          <t>2,971,496</t>
+        </is>
+      </c>
+      <c r="D1476" t="inlineStr">
+        <is>
+          <t>790,613,460</t>
+        </is>
+      </c>
+      <c r="E1476" t="inlineStr">
+        <is>
+          <t>7,631.26</t>
+        </is>
+      </c>
+    </row>
+    <row r="1477">
+      <c r="A1477" t="inlineStr">
+        <is>
+          <t>11 Mar 2026</t>
+        </is>
+      </c>
+      <c r="B1477" t="inlineStr">
+        <is>
+          <t>4854</t>
+        </is>
+      </c>
+      <c r="C1477" t="inlineStr">
+        <is>
+          <t>3,282,977</t>
+        </is>
+      </c>
+      <c r="D1477" t="inlineStr">
+        <is>
+          <t>816,000,053</t>
+        </is>
+      </c>
+      <c r="E1477" t="inlineStr">
+        <is>
+          <t>7,544.78</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BSE/bse_daily.xlsx
+++ b/BSE/bse_daily.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1477"/>
+  <dimension ref="A1:E1489"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40295,6 +40295,330 @@
         </is>
       </c>
     </row>
+    <row r="1478">
+      <c r="A1478" t="inlineStr">
+        <is>
+          <t>12 Mar 2026</t>
+        </is>
+      </c>
+      <c r="B1478" t="inlineStr">
+        <is>
+          <t>4823</t>
+        </is>
+      </c>
+      <c r="C1478" t="inlineStr">
+        <is>
+          <t>3,842,196</t>
+        </is>
+      </c>
+      <c r="D1478" t="inlineStr">
+        <is>
+          <t>879,485,578</t>
+        </is>
+      </c>
+      <c r="E1478" t="inlineStr">
+        <is>
+          <t>8,906.17</t>
+        </is>
+      </c>
+    </row>
+    <row r="1479">
+      <c r="A1479" t="inlineStr">
+        <is>
+          <t>13 Mar 2026</t>
+        </is>
+      </c>
+      <c r="B1479" t="inlineStr">
+        <is>
+          <t>4929</t>
+        </is>
+      </c>
+      <c r="C1479" t="inlineStr">
+        <is>
+          <t>3,814,607</t>
+        </is>
+      </c>
+      <c r="D1479" t="inlineStr">
+        <is>
+          <t>858,815,662</t>
+        </is>
+      </c>
+      <c r="E1479" t="inlineStr">
+        <is>
+          <t>8,802.46</t>
+        </is>
+      </c>
+    </row>
+    <row r="1480">
+      <c r="A1480" t="inlineStr">
+        <is>
+          <t>16 Mar 2026</t>
+        </is>
+      </c>
+      <c r="B1480" t="inlineStr">
+        <is>
+          <t>5072</t>
+        </is>
+      </c>
+      <c r="C1480" t="inlineStr">
+        <is>
+          <t>3,699,340</t>
+        </is>
+      </c>
+      <c r="D1480" t="inlineStr">
+        <is>
+          <t>814,430,474</t>
+        </is>
+      </c>
+      <c r="E1480" t="inlineStr">
+        <is>
+          <t>7,819.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1481">
+      <c r="A1481" t="inlineStr">
+        <is>
+          <t>17 Mar 2026</t>
+        </is>
+      </c>
+      <c r="B1481" t="inlineStr">
+        <is>
+          <t>4848</t>
+        </is>
+      </c>
+      <c r="C1481" t="inlineStr">
+        <is>
+          <t>2,946,691</t>
+        </is>
+      </c>
+      <c r="D1481" t="inlineStr">
+        <is>
+          <t>815,430,459</t>
+        </is>
+      </c>
+      <c r="E1481" t="inlineStr">
+        <is>
+          <t>8,423.78</t>
+        </is>
+      </c>
+    </row>
+    <row r="1482">
+      <c r="A1482" t="inlineStr">
+        <is>
+          <t>18 Mar 2026</t>
+        </is>
+      </c>
+      <c r="B1482" t="inlineStr">
+        <is>
+          <t>4879</t>
+        </is>
+      </c>
+      <c r="C1482" t="inlineStr">
+        <is>
+          <t>3,294,377</t>
+        </is>
+      </c>
+      <c r="D1482" t="inlineStr">
+        <is>
+          <t>773,171,884</t>
+        </is>
+      </c>
+      <c r="E1482" t="inlineStr">
+        <is>
+          <t>8,020.58</t>
+        </is>
+      </c>
+    </row>
+    <row r="1483">
+      <c r="A1483" t="inlineStr">
+        <is>
+          <t>19 Mar 2026</t>
+        </is>
+      </c>
+      <c r="B1483" t="inlineStr">
+        <is>
+          <t>4871</t>
+        </is>
+      </c>
+      <c r="C1483" t="inlineStr">
+        <is>
+          <t>3,685,596</t>
+        </is>
+      </c>
+      <c r="D1483" t="inlineStr">
+        <is>
+          <t>710,715,946</t>
+        </is>
+      </c>
+      <c r="E1483" t="inlineStr">
+        <is>
+          <t>8,198.28</t>
+        </is>
+      </c>
+    </row>
+    <row r="1484">
+      <c r="A1484" t="inlineStr">
+        <is>
+          <t>20 Mar 2026</t>
+        </is>
+      </c>
+      <c r="B1484" t="inlineStr">
+        <is>
+          <t>4864</t>
+        </is>
+      </c>
+      <c r="C1484" t="inlineStr">
+        <is>
+          <t>3,185,715</t>
+        </is>
+      </c>
+      <c r="D1484" t="inlineStr">
+        <is>
+          <t>743,035,898</t>
+        </is>
+      </c>
+      <c r="E1484" t="inlineStr">
+        <is>
+          <t>8,048.39</t>
+        </is>
+      </c>
+    </row>
+    <row r="1485">
+      <c r="A1485" t="inlineStr">
+        <is>
+          <t>23 Mar 2026</t>
+        </is>
+      </c>
+      <c r="B1485" t="inlineStr">
+        <is>
+          <t>5118</t>
+        </is>
+      </c>
+      <c r="C1485" t="inlineStr">
+        <is>
+          <t>5,101,437</t>
+        </is>
+      </c>
+      <c r="D1485" t="inlineStr">
+        <is>
+          <t>937,159,886</t>
+        </is>
+      </c>
+      <c r="E1485" t="inlineStr">
+        <is>
+          <t>10,048.38</t>
+        </is>
+      </c>
+    </row>
+    <row r="1486">
+      <c r="A1486" t="inlineStr">
+        <is>
+          <t>24 Mar 2026</t>
+        </is>
+      </c>
+      <c r="B1486" t="inlineStr">
+        <is>
+          <t>4901</t>
+        </is>
+      </c>
+      <c r="C1486" t="inlineStr">
+        <is>
+          <t>4,265,227</t>
+        </is>
+      </c>
+      <c r="D1486" t="inlineStr">
+        <is>
+          <t>1,005,900,884</t>
+        </is>
+      </c>
+      <c r="E1486" t="inlineStr">
+        <is>
+          <t>10,640.32</t>
+        </is>
+      </c>
+    </row>
+    <row r="1487">
+      <c r="A1487" t="inlineStr">
+        <is>
+          <t>25 Mar 2026</t>
+        </is>
+      </c>
+      <c r="B1487" t="inlineStr">
+        <is>
+          <t>4931</t>
+        </is>
+      </c>
+      <c r="C1487" t="inlineStr">
+        <is>
+          <t>4,476,938</t>
+        </is>
+      </c>
+      <c r="D1487" t="inlineStr">
+        <is>
+          <t>1,179,117,756</t>
+        </is>
+      </c>
+      <c r="E1487" t="inlineStr">
+        <is>
+          <t>12,181.02</t>
+        </is>
+      </c>
+    </row>
+    <row r="1488">
+      <c r="A1488" t="inlineStr">
+        <is>
+          <t>27 Mar 2026</t>
+        </is>
+      </c>
+      <c r="B1488" t="inlineStr">
+        <is>
+          <t>5037</t>
+        </is>
+      </c>
+      <c r="C1488" t="inlineStr">
+        <is>
+          <t>4,910,454</t>
+        </is>
+      </c>
+      <c r="D1488" t="inlineStr">
+        <is>
+          <t>1,493,176,062</t>
+        </is>
+      </c>
+      <c r="E1488" t="inlineStr">
+        <is>
+          <t>12,496.51</t>
+        </is>
+      </c>
+    </row>
+    <row r="1489">
+      <c r="A1489" t="inlineStr">
+        <is>
+          <t>30 Mar 2026</t>
+        </is>
+      </c>
+      <c r="B1489" t="inlineStr">
+        <is>
+          <t>5102</t>
+        </is>
+      </c>
+      <c r="C1489" t="inlineStr">
+        <is>
+          <t>5,189,126</t>
+        </is>
+      </c>
+      <c r="D1489" t="inlineStr">
+        <is>
+          <t>1,258,077,225</t>
+        </is>
+      </c>
+      <c r="E1489" t="inlineStr">
+        <is>
+          <t>10,503.06</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BSE/bse_daily.xlsx
+++ b/BSE/bse_daily.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1489"/>
+  <dimension ref="A1:E1493"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40619,6 +40619,114 @@
         </is>
       </c>
     </row>
+    <row r="1490">
+      <c r="A1490" t="inlineStr">
+        <is>
+          <t>01 Apr 2026</t>
+        </is>
+      </c>
+      <c r="B1490" t="inlineStr">
+        <is>
+          <t>4920</t>
+        </is>
+      </c>
+      <c r="C1490" t="inlineStr">
+        <is>
+          <t>4,024,428</t>
+        </is>
+      </c>
+      <c r="D1490" t="inlineStr">
+        <is>
+          <t>1,037,088,361</t>
+        </is>
+      </c>
+      <c r="E1490" t="inlineStr">
+        <is>
+          <t>8,939.53</t>
+        </is>
+      </c>
+    </row>
+    <row r="1491">
+      <c r="A1491" t="inlineStr">
+        <is>
+          <t>02 Apr 2026</t>
+        </is>
+      </c>
+      <c r="B1491" t="inlineStr">
+        <is>
+          <t>4836</t>
+        </is>
+      </c>
+      <c r="C1491" t="inlineStr">
+        <is>
+          <t>4,009,350</t>
+        </is>
+      </c>
+      <c r="D1491" t="inlineStr">
+        <is>
+          <t>907,679,072</t>
+        </is>
+      </c>
+      <c r="E1491" t="inlineStr">
+        <is>
+          <t>8,541.27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1492">
+      <c r="A1492" t="inlineStr">
+        <is>
+          <t>06 Apr 2026</t>
+        </is>
+      </c>
+      <c r="B1492" t="inlineStr">
+        <is>
+          <t>5038</t>
+        </is>
+      </c>
+      <c r="C1492" t="inlineStr">
+        <is>
+          <t>4,047,771</t>
+        </is>
+      </c>
+      <c r="D1492" t="inlineStr">
+        <is>
+          <t>964,191,418</t>
+        </is>
+      </c>
+      <c r="E1492" t="inlineStr">
+        <is>
+          <t>8,507.39</t>
+        </is>
+      </c>
+    </row>
+    <row r="1493">
+      <c r="A1493" t="inlineStr">
+        <is>
+          <t>07 Apr 2026</t>
+        </is>
+      </c>
+      <c r="B1493" t="inlineStr">
+        <is>
+          <t>4835</t>
+        </is>
+      </c>
+      <c r="C1493" t="inlineStr">
+        <is>
+          <t>3,185,818</t>
+        </is>
+      </c>
+      <c r="D1493" t="inlineStr">
+        <is>
+          <t>678,815,568</t>
+        </is>
+      </c>
+      <c r="E1493" t="inlineStr">
+        <is>
+          <t>6,474.51</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
